--- a/reports/二级子公司D_利润表_2026-11.xlsx
+++ b/reports/二级子公司D_利润表_2026-11.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>83079738</v>
+        <v>85173082</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>81249318</v>
+        <v>81546836</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>948006642</v>
+        <v>948180492</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>280697</v>
+        <v>280261</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3209891</v>
+        <v>3213707</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>238478</v>
+        <v>239623</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2749698</v>
+        <v>2754148</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>199508</v>
+        <v>199209</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2293239</v>
+        <v>2294330</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>180912</v>
+        <v>178956</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2064592</v>
+        <v>2063937</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>99866</v>
+        <v>99321</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1145955</v>
+        <v>1146054</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>79462</v>
+        <v>79461</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>916744</v>
+        <v>916431</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>82000815</v>
+        <v>84096251</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>80170395</v>
+        <v>80470005</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4477582</v>
+        <v>4494027</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>51557103</v>
+        <v>51529829</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>348410</v>
+        <v>350407</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>4012240</v>
+        <v>4008975</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>602643</v>
+        <v>601974</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6882471</v>
+        <v>6875433</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>72069129</v>
+        <v>72336936</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>842564037</v>
+        <v>842727817</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1191804</v>
+        <v>1206105</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>13749204</v>
+        <v>13764355</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>399693</v>
+        <v>401777</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4587179</v>
+        <v>4589886</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2009972</v>
+        <v>2005712</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>22937540</v>
+        <v>22954469</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>498495</v>
+        <v>500305</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>5729108</v>
+        <v>5738703</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1789061</v>
+        <v>1796575</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>20629691</v>
+        <v>20655359</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>41359</v>
+        <v>41062</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>453476</v>
+        <v>453489</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1073534</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>12382805</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>715075</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>8251072</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>54468744</v>
+        <v>58228629</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>48859264</v>
+        <v>48733944</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>47965417</v>
+        <v>47834835</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>550087207</v>
+        <v>549608122</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>893847</v>
+        <v>899109</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>10312903</v>
+        <v>10306233</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1802657</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>20618592</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>578030</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>6600836</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>361726</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>4127586</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>434187</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4955459</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>325387</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3717957</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>216559</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2479117</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>180051</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2065903</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>848818</v>
+        <v>848101</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>9747240</v>
+        <v>9753532</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>653297</v>
+        <v>647066</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>7455016</v>
+        <v>7455715</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>498792</v>
+        <v>496921</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>5729330</v>
+        <v>5732396</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3775821</v>
+        <v>3773871</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>43549158</v>
+        <v>43544554</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>155018</v>
+        <v>149019</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1700484</v>
+        <v>1718137</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>331031</v>
+        <v>328176</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3626295</v>
+        <v>3621048</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>369016</v>
+        <v>328176</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4076175</v>
+        <v>3621048</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>41088</v>
+        <v>41210</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>453213</v>
+        <v>452679</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>167308</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1834029</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>316180</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3610066</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>111885</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1223991</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>83924</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>918454</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>139746</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1531321</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>451039</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>5164884</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>74223</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>816781</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>55528</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>612411</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>92340</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1020214</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>64539</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>713758</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>46072</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>509551</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>36875</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>407462</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27697</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>305518</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>27532071</v>
+        <v>26987121</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31593040</v>
+        <v>29919178</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>180374</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2062077</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>46575</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>509750</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>71865</v>
+        <v>72523</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>793068</v>
+        <v>793384</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>27460206</v>
+        <v>27094972</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2578639</v>
+        <v>2587394</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>28320066</v>
+        <v>28358763</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>24881567</v>
+        <v>24507578</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>24881567</v>
+        <v>24507578</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>24881567</v>
+        <v>24507578</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>24881567</v>
+        <v>24507578</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>24881567</v>
+        <v>24507578</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
